--- a/artfynd/A 61288-2025 artfynd.xlsx
+++ b/artfynd/A 61288-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>130246270</v>
       </c>
       <c r="B2" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>130246275</v>
       </c>
       <c r="B3" t="n">
-        <v>75201</v>
+        <v>75286</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>130246271</v>
       </c>
       <c r="B4" t="n">
-        <v>58113</v>
+        <v>58198</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>130246274</v>
       </c>
       <c r="B5" t="n">
-        <v>75201</v>
+        <v>75286</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>130246269</v>
       </c>
       <c r="B6" t="n">
-        <v>75201</v>
+        <v>75286</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>130246273</v>
       </c>
       <c r="B7" t="n">
-        <v>75201</v>
+        <v>75286</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,6 +1331,121 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130270388</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98920</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Riala-Sättra, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>692003</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6612496</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>38 st bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61288-2025 artfynd.xlsx
+++ b/artfynd/A 61288-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130246270</v>
       </c>
       <c r="B2" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>130246275</v>
       </c>
       <c r="B3" t="n">
-        <v>75286</v>
+        <v>75289</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>130246274</v>
       </c>
       <c r="B5" t="n">
-        <v>75286</v>
+        <v>75289</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>130246269</v>
       </c>
       <c r="B6" t="n">
-        <v>75286</v>
+        <v>75289</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>130246273</v>
       </c>
       <c r="B7" t="n">
-        <v>75286</v>
+        <v>75289</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>130270388</v>
       </c>
       <c r="B8" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 61288-2025 artfynd.xlsx
+++ b/artfynd/A 61288-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130246270</v>
       </c>
       <c r="B2" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130246275</v>
+        <v>130246271</v>
       </c>
       <c r="B3" t="n">
-        <v>75289</v>
+        <v>58224</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -810,21 +810,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6426</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>692009</v>
+        <v>692051</v>
       </c>
       <c r="R3" t="n">
-        <v>6612456</v>
+        <v>6612462</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +869,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130246271</v>
+        <v>130246275</v>
       </c>
       <c r="B4" t="n">
-        <v>58198</v>
+        <v>75315</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,21 +917,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>692051</v>
+        <v>692009</v>
       </c>
       <c r="R4" t="n">
-        <v>6612462</v>
+        <v>6612456</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,7 +976,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,7 +1016,7 @@
         <v>130246274</v>
       </c>
       <c r="B5" t="n">
-        <v>75289</v>
+        <v>75315</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>130246269</v>
       </c>
       <c r="B6" t="n">
-        <v>75289</v>
+        <v>75315</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>130246273</v>
       </c>
       <c r="B7" t="n">
-        <v>75289</v>
+        <v>75315</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>130270388</v>
       </c>
       <c r="B8" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 61288-2025 artfynd.xlsx
+++ b/artfynd/A 61288-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130246270</v>
       </c>
       <c r="B2" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130246271</v>
+        <v>130246275</v>
       </c>
       <c r="B3" t="n">
-        <v>58224</v>
+        <v>75315</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -810,21 +810,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>6426</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>692051</v>
+        <v>692009</v>
       </c>
       <c r="R3" t="n">
-        <v>6612462</v>
+        <v>6612456</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +869,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130246275</v>
+        <v>130246271</v>
       </c>
       <c r="B4" t="n">
-        <v>75315</v>
+        <v>58224</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,21 +917,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6426</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>692009</v>
+        <v>692051</v>
       </c>
       <c r="R4" t="n">
-        <v>6612456</v>
+        <v>6612462</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,7 +976,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1337,7 +1337,7 @@
         <v>130270388</v>
       </c>
       <c r="B8" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 61288-2025 artfynd.xlsx
+++ b/artfynd/A 61288-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130246270</v>
       </c>
       <c r="B2" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>130270388</v>
       </c>
       <c r="B8" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 61288-2025 artfynd.xlsx
+++ b/artfynd/A 61288-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130246270</v>
       </c>
       <c r="B2" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130246275</v>
+        <v>130246271</v>
       </c>
       <c r="B3" t="n">
-        <v>75315</v>
+        <v>58226</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -810,21 +810,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6426</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>692009</v>
+        <v>692051</v>
       </c>
       <c r="R3" t="n">
-        <v>6612456</v>
+        <v>6612462</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +869,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130246271</v>
+        <v>130246275</v>
       </c>
       <c r="B4" t="n">
-        <v>58224</v>
+        <v>75317</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,21 +917,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>692051</v>
+        <v>692009</v>
       </c>
       <c r="R4" t="n">
-        <v>6612462</v>
+        <v>6612456</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,7 +976,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,7 +1016,7 @@
         <v>130246274</v>
       </c>
       <c r="B5" t="n">
-        <v>75315</v>
+        <v>75317</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>130246269</v>
       </c>
       <c r="B6" t="n">
-        <v>75315</v>
+        <v>75317</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>130246273</v>
       </c>
       <c r="B7" t="n">
-        <v>75315</v>
+        <v>75317</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>130270388</v>
       </c>
       <c r="B8" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 61288-2025 artfynd.xlsx
+++ b/artfynd/A 61288-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130246270</v>
       </c>
       <c r="B2" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130246271</v>
+        <v>130246275</v>
       </c>
       <c r="B3" t="n">
-        <v>58226</v>
+        <v>75317</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -810,21 +810,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>6426</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>692051</v>
+        <v>692009</v>
       </c>
       <c r="R3" t="n">
-        <v>6612462</v>
+        <v>6612456</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +869,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130246275</v>
+        <v>130246271</v>
       </c>
       <c r="B4" t="n">
-        <v>75317</v>
+        <v>58226</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,21 +917,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6426</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>692009</v>
+        <v>692051</v>
       </c>
       <c r="R4" t="n">
-        <v>6612456</v>
+        <v>6612462</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,7 +976,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1337,7 +1337,7 @@
         <v>130270388</v>
       </c>
       <c r="B8" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 61288-2025 artfynd.xlsx
+++ b/artfynd/A 61288-2025 artfynd.xlsx
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130246275</v>
+        <v>130246271</v>
       </c>
       <c r="B3" t="n">
-        <v>75317</v>
+        <v>58226</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -810,21 +810,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6426</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>692009</v>
+        <v>692051</v>
       </c>
       <c r="R3" t="n">
-        <v>6612456</v>
+        <v>6612462</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +869,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130246271</v>
+        <v>130246275</v>
       </c>
       <c r="B4" t="n">
-        <v>58226</v>
+        <v>75317</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,21 +917,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>692051</v>
+        <v>692009</v>
       </c>
       <c r="R4" t="n">
-        <v>6612462</v>
+        <v>6612456</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,7 +976,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 61288-2025 artfynd.xlsx
+++ b/artfynd/A 61288-2025 artfynd.xlsx
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130246271</v>
+        <v>130246275</v>
       </c>
       <c r="B3" t="n">
-        <v>58226</v>
+        <v>75317</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -810,21 +810,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>6426</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>692051</v>
+        <v>692009</v>
       </c>
       <c r="R3" t="n">
-        <v>6612462</v>
+        <v>6612456</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +869,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130246275</v>
+        <v>130246271</v>
       </c>
       <c r="B4" t="n">
-        <v>75317</v>
+        <v>58226</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,21 +917,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6426</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>692009</v>
+        <v>692051</v>
       </c>
       <c r="R4" t="n">
-        <v>6612456</v>
+        <v>6612462</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,7 +976,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 61288-2025 artfynd.xlsx
+++ b/artfynd/A 61288-2025 artfynd.xlsx
@@ -1337,7 +1337,7 @@
         <v>130270388</v>
       </c>
       <c r="B8" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
